--- a/resources/空模板.xlsx
+++ b/resources/空模板.xlsx
@@ -3754,7 +3754,7 @@
       <formula2/>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="选择需要帮帮的难度和目标" sqref="E7:E1048576">
-      <formula1>"困难满原石,困难满花,卓越满原石,卓越满花,月谕满原石,月谕满花,"</formula1>
+      <formula1>"困难模式满原石,困难模式满星章,卓越模式满原石,卓越模式满星章,月谕模式满原石,月谕模式满星章,"</formula1>
       <formula2/>
     </dataValidation>
   </dataValidations>
@@ -7125,7 +7125,7 @@
       <formula2/>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" prompt="选择需要帮帮的难度和目标" sqref="E8:E1048576">
-      <formula1>"11层满星,12层满星,"</formula1>
+      <formula1>"第11层满星,第12层满星,"</formula1>
       <formula2/>
     </dataValidation>
   </dataValidations>
